--- a/Outputs/Scenarios/PtX_demand_PL_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_PL_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.01032955500440896</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00621949830417308</v>
+        <v>0.003376484447995585</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.002073166101391027</v>
+        <v>0.004892542241271683</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>0.0001488314026094087</v>
       </c>
       <c r="K28" t="n">
-        <v>0.002073166101391027</v>
+        <v>0.002096803817687864</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.01529164859790063</v>
       </c>
       <c r="K30" t="n">
-        <v>0.03356529316898466</v>
+        <v>0.01822215954322981</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.01118843105632822</v>
+        <v>0.02640399701688789</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0.000804823610415823</v>
       </c>
       <c r="K42" t="n">
-        <v>0.01118843105632822</v>
+        <v>0.01131599872152338</v>
       </c>
     </row>
     <row r="43">
